--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0003T0006Z000C1N62_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0003T0006Z000C1N62_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.56695399969992</v>
+        <v>4.154630024951238</v>
       </c>
       <c r="D2" t="n">
-        <v>12.4598971949353</v>
+        <v>2.024733294176987</v>
       </c>
       <c r="E2" t="n">
-        <v>15.66295453462804</v>
+        <v>2.545230111877057</v>
       </c>
       <c r="F2" t="n">
-        <v>11.43761179588954</v>
+        <v>1.85861191683205</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>70.60030324422767</v>
+        <v>11.472549277187</v>
       </c>
       <c r="D3" t="n">
-        <v>6.104564623841874</v>
+        <v>0.9919917513743046</v>
       </c>
       <c r="E3" t="n">
-        <v>15.66295453462804</v>
+        <v>2.545230111877057</v>
       </c>
       <c r="F3" t="n">
-        <v>11.43761179588954</v>
+        <v>1.85861191683205</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>52.52453235594798</v>
+        <v>8.535236507841546</v>
       </c>
       <c r="D4" t="n">
-        <v>20.22405364112279</v>
+        <v>3.286408716682454</v>
       </c>
       <c r="E4" t="n">
-        <v>15.66295453462804</v>
+        <v>2.545230111877057</v>
       </c>
       <c r="F4" t="n">
-        <v>11.43761179588954</v>
+        <v>1.85861191683205</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>44.24497968958584</v>
+        <v>7.1898091995577</v>
       </c>
       <c r="D5" t="n">
-        <v>44.5701693961331</v>
+        <v>7.24265252687163</v>
       </c>
       <c r="E5" t="n">
-        <v>15.66295453462804</v>
+        <v>2.545230111877057</v>
       </c>
       <c r="F5" t="n">
-        <v>11.43761179588954</v>
+        <v>1.85861191683205</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>22.55673259670167</v>
+        <v>3.665469046964021</v>
       </c>
       <c r="D6" t="n">
-        <v>23.10510285137771</v>
+        <v>3.754579213348878</v>
       </c>
       <c r="E6" t="n">
-        <v>15.66295453462804</v>
+        <v>2.545230111877057</v>
       </c>
       <c r="F6" t="n">
-        <v>11.43761179588954</v>
+        <v>1.85861191683205</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>51.81797764298625</v>
+        <v>8.420421366985266</v>
       </c>
       <c r="D7" t="n">
-        <v>15.40292180074936</v>
+        <v>2.502974792621771</v>
       </c>
       <c r="E7" t="n">
-        <v>15.66295453462804</v>
+        <v>2.545230111877057</v>
       </c>
       <c r="F7" t="n">
-        <v>11.43761179588954</v>
+        <v>1.85861191683205</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>35.00584680251012</v>
+        <v>5.688450105407894</v>
       </c>
       <c r="D8" t="n">
-        <v>14.21449139022655</v>
+        <v>2.309854850911814</v>
       </c>
       <c r="E8" t="n">
-        <v>15.66295453462804</v>
+        <v>2.545230111877057</v>
       </c>
       <c r="F8" t="n">
-        <v>11.43761179588954</v>
+        <v>1.85861191683205</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
